--- a/docs/Mapping_casi_uso/unioni_civili/UnCiv_998_5.xlsx
+++ b/docs/Mapping_casi_uso/unioni_civili/UnCiv_998_5.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="74">
   <si>
     <t>Sezione</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>descrizioneMotivoRecupero</t>
+  </si>
+  <si>
+    <t>Identificativo Atto Cartaceo</t>
+  </si>
+  <si>
+    <t>idAttoCartaceo</t>
   </si>
   <si>
     <t>Atto di riferimento</t>
@@ -286,7 +292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="24.91796875" customWidth="true" bestFit="true"/>
@@ -576,19 +582,19 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
@@ -599,16 +605,16 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>40</v>
@@ -622,7 +628,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>41</v>
@@ -631,7 +637,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -645,7 +651,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>43</v>
@@ -654,7 +660,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -668,7 +674,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
@@ -677,7 +683,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -691,16 +697,16 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -714,19 +720,19 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>10</v>
@@ -737,19 +743,19 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
@@ -760,7 +766,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>52</v>
@@ -769,10 +775,10 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>10</v>
@@ -783,19 +789,19 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>10</v>
@@ -806,7 +812,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>55</v>
@@ -815,7 +821,7 @@
         <v>25</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>56</v>
@@ -829,7 +835,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>57</v>
@@ -838,7 +844,7 @@
         <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>58</v>
@@ -852,16 +858,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>60</v>
@@ -875,59 +881,59 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="F26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>14</v>
@@ -944,24 +950,47 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="B30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>16</v>
       </c>
     </row>
